--- a/site/mb_leads.xlsx
+++ b/site/mb_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pendennis Shaft</t>
+          <t>Mack Shaft</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MBMINE-Pendennis Shaft</t>
+          <t>MBMINE-Mack Shaft</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1952,19 +1952,19 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U22" t="n">
         <v>20</v>
       </c>
       <c r="V22" t="n">
-        <v>50.97194</v>
+        <v>54.87167</v>
       </c>
       <c r="W22" t="n">
-        <v>-95.68868999999999</v>
+        <v>-100.84001</v>
       </c>
       <c r="X22" t="inlineStr"/>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mack Shaft</t>
+          <t>Moose Horn (Ballast) Mine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MBMINE-Mack Shaft</t>
+          <t>MBMINE-Moose Horn (Ballast) Mine</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2020,19 +2020,19 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>20</v>
       </c>
       <c r="V23" t="n">
-        <v>54.87167</v>
+        <v>51.24034</v>
       </c>
       <c r="W23" t="n">
-        <v>-100.84001</v>
+        <v>-98.38051</v>
       </c>
       <c r="X23" t="inlineStr"/>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Moose Horn (Ballast) Mine</t>
+          <t>J.V. Shaft #1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MBMINE-Moose Horn (Ballast) Mine</t>
+          <t>MBMINE-J.V. Shaft #1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2097,80 +2097,12 @@
         <v>20</v>
       </c>
       <c r="V24" t="n">
-        <v>51.24034</v>
+        <v>49.87102</v>
       </c>
       <c r="W24" t="n">
-        <v>-98.38051</v>
+        <v>-95.60503</v>
       </c>
       <c r="X24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>J.V. Shaft #1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MBMINE-J.V. Shaft #1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>20</v>
-      </c>
-      <c r="V25" t="n">
-        <v>49.87102</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-95.60503</v>
-      </c>
-      <c r="X25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
